--- a/BOM/PDU_Resistors_Board_VER1.0.xlsx
+++ b/BOM/PDU_Resistors_Board_VER1.0.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\PDU_Resistors_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDE81F2-0707-489C-A90B-A7BEBBA72972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58101BA-E0E9-4FC0-B921-273F32833594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Reference</t>
   </si>
@@ -68,25 +68,52 @@
   </si>
   <si>
     <t>Resistor_THT:R_Axial_Power_L60.0mm_W14.0mm_P66.04mm</t>
+  </si>
+  <si>
+    <t>Connector</t>
+  </si>
+  <si>
+    <t>Resistor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -116,9 +143,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -426,43 +459,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -473,7 +506,9 @@
         <v>10</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
@@ -482,7 +517,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -493,7 +528,9 @@
         <v>14</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
